--- a/diseases/d020/2015-2019.xlsx
+++ b/diseases/d020/2015-2019.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2390,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3571,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4761,9 +4752,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6093,9 +6081,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7277,9 +7262,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -8609,9 +8591,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10089,9 +10068,6 @@
       <c r="O65" t="n">
         <v>5</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.009807015297364935</v>
       </c>
@@ -11273,9 +11249,6 @@
       <c r="O73" t="n">
         <v>13</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.02549823977314883</v>
       </c>
@@ -12605,9 +12578,6 @@
       <c r="O82" t="n">
         <v>18</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.03530525507051377</v>
       </c>
@@ -13937,9 +13907,6 @@
       <c r="O91" t="n">
         <v>4</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.007845612237891948</v>
       </c>
@@ -15269,9 +15236,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -16601,9 +16565,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17785,9 +17746,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18969,9 +18927,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -20301,9 +20256,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -21485,9 +21437,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -22817,9 +22766,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -24297,9 +24243,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -25629,9 +25572,6 @@
       <c r="O170" t="n">
         <v>1</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -26813,9 +26753,6 @@
       <c r="O178" t="n">
         <v>11</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.02144339842463929</v>
       </c>
@@ -28293,9 +28230,6 @@
       <c r="O188" t="n">
         <v>14</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.02729159799499546</v>
       </c>
@@ -29625,9 +29559,6 @@
       <c r="O197" t="n">
         <v>2</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.00389879971357078</v>
       </c>
@@ -30809,9 +30740,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -32141,9 +32069,6 @@
       <c r="O214" t="n">
         <v>1</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -33325,9 +33250,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -34509,9 +34431,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -35841,9 +35760,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -37025,9 +36941,6 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
@@ -38357,9 +38270,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -39837,9 +39747,6 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
@@ -41169,9 +41076,6 @@
       <c r="O275" t="n">
         <v>2</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.003884530731352934</v>
       </c>
@@ -42501,9 +42405,6 @@
       <c r="O284" t="n">
         <v>1</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -43833,9 +43734,6 @@
       <c r="O293" t="n">
         <v>5</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.009711326828382336</v>
       </c>
@@ -45017,9 +44915,6 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -46349,9 +46244,6 @@
       <c r="O310" t="n">
         <v>0</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0</v>
       </c>
@@ -47533,9 +47425,6 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
@@ -48717,9 +48606,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -49901,9 +49787,6 @@
       <c r="O334" t="n">
         <v>0</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0</v>
       </c>
@@ -51233,9 +51116,6 @@
       <c r="O343" t="n">
         <v>0</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0</v>
       </c>
@@ -52417,9 +52297,6 @@
       <c r="O351" t="n">
         <v>0</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0</v>
       </c>
@@ -53897,9 +53774,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -55229,9 +55103,6 @@
       <c r="O370" t="n">
         <v>1</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -56561,9 +56432,6 @@
       <c r="O379" t="n">
         <v>3</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0.005809349466335731</v>
       </c>
@@ -58041,9 +57909,6 @@
       <c r="O389" t="n">
         <v>12</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>0.02323739786534292</v>
       </c>
@@ -59373,9 +59238,6 @@
       <c r="O398" t="n">
         <v>1</v>
       </c>
-      <c r="Q398" t="n">
-        <v>0</v>
-      </c>
       <c r="R398" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -60557,9 +60419,6 @@
       <c r="O406" t="n">
         <v>0</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0</v>
       </c>
@@ -62037,9 +61896,6 @@
       <c r="O416" t="n">
         <v>0</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0</v>
       </c>
@@ -63221,9 +63077,6 @@
       <c r="O424" t="n">
         <v>0</v>
       </c>
-      <c r="Q424" t="n">
-        <v>0</v>
-      </c>
       <c r="R424" t="n">
         <v>0</v>
       </c>
@@ -64553,9 +64406,6 @@
       <c r="O433" t="n">
         <v>0</v>
       </c>
-      <c r="Q433" t="n">
-        <v>0</v>
-      </c>
       <c r="R433" t="n">
         <v>0</v>
       </c>
@@ -65737,9 +65587,6 @@
       <c r="O441" t="n">
         <v>0</v>
       </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
       <c r="R441" t="n">
         <v>0</v>
       </c>
@@ -66921,9 +66768,6 @@
       <c r="O449" t="n">
         <v>0</v>
       </c>
-      <c r="Q449" t="n">
-        <v>0</v>
-      </c>
       <c r="R449" t="n">
         <v>0</v>
       </c>
@@ -68105,9 +67949,6 @@
       <c r="O457" t="n">
         <v>0</v>
       </c>
-      <c r="Q457" t="n">
-        <v>0</v>
-      </c>
       <c r="R457" t="n">
         <v>0</v>
       </c>
@@ -69585,9 +69426,6 @@
       <c r="O467" t="n">
         <v>0</v>
       </c>
-      <c r="Q467" t="n">
-        <v>0</v>
-      </c>
       <c r="R467" t="n">
         <v>0</v>
       </c>
@@ -70917,9 +70755,6 @@
       <c r="O476" t="n">
         <v>0</v>
       </c>
-      <c r="Q476" t="n">
-        <v>0</v>
-      </c>
       <c r="R476" t="n">
         <v>0</v>
       </c>
@@ -72249,9 +72084,6 @@
       <c r="O485" t="n">
         <v>3</v>
       </c>
-      <c r="Q485" t="n">
-        <v>0</v>
-      </c>
       <c r="R485" t="n">
         <v>0.005795103006603752</v>
       </c>
@@ -73729,9 +73561,6 @@
       <c r="O495" t="n">
         <v>15</v>
       </c>
-      <c r="Q495" t="n">
-        <v>0</v>
-      </c>
       <c r="R495" t="n">
         <v>0.02897551503301876</v>
       </c>
@@ -75061,9 +74890,6 @@
       <c r="O504" t="n">
         <v>13</v>
       </c>
-      <c r="Q504" t="n">
-        <v>0</v>
-      </c>
       <c r="R504" t="n">
         <v>0.02511211302861626</v>
       </c>
@@ -76393,9 +76219,6 @@
       <c r="O513" t="n">
         <v>2</v>
       </c>
-      <c r="Q513" t="n">
-        <v>0</v>
-      </c>
       <c r="R513" t="n">
         <v>0.003863402004402502</v>
       </c>
@@ -77576,9 +77399,6 @@
       </c>
       <c r="O521" t="n">
         <v>1</v>
-      </c>
-      <c r="Q521" t="n">
-        <v>0</v>
       </c>
       <c r="R521" t="n">
         <v>0.001931701002201251</v>
